--- a/Supporting_Documents/Game_Play_History_정재우.xlsx
+++ b/Supporting_Documents/Game_Play_History_정재우.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="240">
   <si>
     <t>플레이 증빙</t>
   </si>
@@ -39,9 +39,6 @@
   </si>
   <si>
     <t>던전앤파이터 모바일</t>
-  </si>
-  <si>
-    <t>정재우 | 게임 플레이 이력</t>
   </si>
   <si>
     <t>Lv.64
@@ -51,19 +48,10 @@
     <t>리그 오브 레전드 (League of Legends)</t>
   </si>
   <si>
-    <t>게임 플레이 경험 요약</t>
-  </si>
-  <si>
-    <t>총 게임 수</t>
-  </si>
-  <si>
     <t>2013~2019 프로 선수·코치·감독 활동</t>
   </si>
   <si>
     <t>메이플스토리</t>
-  </si>
-  <si>
-    <t>완료 엔딩</t>
   </si>
   <si>
     <t>3672시간 59분 / 증빙 캡처 당시 Lv.287 / 유니온 Lv.9139
@@ -79,9 +67,6 @@
     <t>명일방주: 엔드필드 (Arknights: Endfield)</t>
   </si>
   <si>
-    <t>경험 플랫폼</t>
-  </si>
-  <si>
     <t>Lv.20 / 탐색 레벨 2</t>
   </si>
   <si>
@@ -97,9 +82,6 @@
     <t>넥슨 이벤트 조회 기록 (과거 게임 내역 누락 존재)</t>
   </si>
   <si>
-    <t>경험 장르</t>
-  </si>
-  <si>
     <t>삼국지: 천하결전</t>
   </si>
   <si>
@@ -160,7 +142,7 @@
     <t>DAVE THE DIVER</t>
   </si>
   <si>
-    <t>본편 엔딩 / In the Jungle DLC 엔딩</t>
+    <t>44.9시간 / 본편 엔딩 / In the Jungle DLC 엔딩</t>
   </si>
   <si>
     <t>Detroit: Become Human</t>
@@ -191,7 +173,7 @@
     <t>Grand Theft Auto V</t>
   </si>
   <si>
-    <t>Steam 플레이 시간 / 본편 엔딩</t>
+    <t>100.6시간 / 본편 엔딩</t>
   </si>
   <si>
     <t>Heavy Rain</t>
@@ -333,9 +315,6 @@
     <t>Trine 4: The Nightmare Prince</t>
   </si>
   <si>
-    <t>PC</t>
-  </si>
-  <si>
     <t>Unrailed!</t>
   </si>
   <si>
@@ -355,24 +334,57 @@
     <t>World War Z</t>
   </si>
   <si>
+    <t>REPLACED</t>
+  </si>
+  <si>
+    <t>Steam 플레이 기록도전과제 18/34</t>
+  </si>
+  <si>
+    <t>산나비</t>
+  </si>
+  <si>
+    <t>Steam 플레이 시간 7시간 12분 / 본편 엔딩 / 도전 과제 12/21 달성</t>
+  </si>
+  <si>
+    <t>The Quarry</t>
+  </si>
+  <si>
+    <t>Steam 8시간 / 본편 엔딩 / 도전 과제 19/40 (47%) / 챕터 10 완료</t>
+  </si>
+  <si>
+    <t>제우스: 오만의 신</t>
+  </si>
+  <si>
+    <t>오픈 3일차 랭킹 캡처 당시 Lv.26 / 클래스 30위 / 전체 231위 / 현재 Lv.28 / 약 10만원 과금</t>
+  </si>
+  <si>
+    <t>정재우 | 게임 플레이 이력</t>
+  </si>
+  <si>
+    <t>게임 플레이 경험 요약</t>
+  </si>
+  <si>
+    <t>총 게임 수</t>
+  </si>
+  <si>
+    <t>완료 엔딩</t>
+  </si>
+  <si>
+    <t>경험 플랫폼</t>
+  </si>
+  <si>
+    <t>경험 장르</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
     <t>시뮬레이션</t>
   </si>
   <si>
-    <t>REPLACED</t>
-  </si>
-  <si>
     <t>Mobile</t>
   </si>
   <si>
-    <t>Steam 플레이 기록도전과제 18/34</t>
-  </si>
-  <si>
-    <t>산나비</t>
-  </si>
-  <si>
-    <t>Steam 플레이 시간 7시간 12분 / 본편 엔딩 / 도전 과제 12/21 달성</t>
-  </si>
-  <si>
     <t>RPG</t>
   </si>
   <si>
@@ -568,6 +580,9 @@
     <t>액션 / 플랫폼</t>
   </si>
   <si>
+    <t>어드벤처 / 인터랙티브 호러</t>
+  </si>
+  <si>
     <t>액션 / 플랫포머</t>
   </si>
   <si>
@@ -713,6 +728,15 @@
   </si>
   <si>
     <t>시즌2 북미서버 랭커</t>
+  </si>
+  <si>
+    <t>MMORPG / 리니지라이크</t>
+  </si>
+  <si>
+    <t>Lv.28</t>
+  </si>
+  <si>
+    <t>오픈 3일차 / 약 10만원 과금</t>
   </si>
 </sst>
 </file>
@@ -763,6 +787,21 @@
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
       <sz val="20.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Malgun Gothic"/>
@@ -799,21 +838,6 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
-    </font>
-    <font>
-      <b/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Carlito"/>
     </font>
     <font>
       <b/>
@@ -894,6 +918,11 @@
       </bottom>
     </border>
     <border>
+      <top style="thin">
+        <color rgb="FFD9E0E6"/>
+      </top>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFD9E0E6"/>
       </left>
@@ -914,11 +943,6 @@
       <bottom style="thin">
         <color rgb="FFD9E0E6"/>
       </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FFD9E0E6"/>
-      </top>
     </border>
     <border>
       <bottom style="thin">
@@ -957,9 +981,6 @@
     <xf borderId="2" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf borderId="2" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -969,43 +990,46 @@
     <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="6" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="6" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="4" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="4" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="4" fontId="13" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="12" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="4" fontId="14" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="15" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf borderId="6" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1064,7 +1088,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0">
+              <a:defRPr b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -1072,7 +1096,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0">
+              <a:rPr b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -1110,11 +1134,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="1220921654"/>
-        <c:axId val="876660282"/>
+        <c:axId val="325997577"/>
+        <c:axId val="838849254"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1220921654"/>
+        <c:axId val="325997577"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1170,10 +1194,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="876660282"/>
+        <c:crossAx val="838849254"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="876660282"/>
+        <c:axId val="838849254"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1239,7 +1263,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1220921654"/>
+        <c:crossAx val="325997577"/>
         <c:crosses val="max"/>
       </c:valAx>
     </c:plotArea>
@@ -1276,7 +1300,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr lvl="0">
-              <a:defRPr b="0">
+              <a:defRPr b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -1284,7 +1308,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="0">
+              <a:rPr b="0" i="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -1437,7 +1461,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image12.jpg"/>
+        <xdr:cNvPr id="0" name="image27.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1465,7 +1489,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image33.jpg"/>
+        <xdr:cNvPr id="0" name="image21.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1493,7 +1517,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image110.jpg"/>
+        <xdr:cNvPr id="0" name="image44.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1521,7 +1545,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image102.jpg"/>
+        <xdr:cNvPr id="0" name="image14.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1549,7 +1573,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPr id="0" name="image84.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1577,7 +1601,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image32.jpg"/>
+        <xdr:cNvPr id="0" name="image39.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1605,7 +1629,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image45.jpg"/>
+        <xdr:cNvPr id="0" name="image9.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1633,7 +1657,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPr id="0" name="image32.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1661,7 +1685,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image9.jpg"/>
+        <xdr:cNvPr id="0" name="image51.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1689,7 +1713,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image38.jpg"/>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1717,7 +1741,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image30.jpg"/>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1745,7 +1769,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image105.jpg"/>
+        <xdr:cNvPr id="0" name="image7.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1773,7 +1797,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPr id="0" name="image33.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1801,7 +1825,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image13.jpg"/>
+        <xdr:cNvPr id="0" name="image69.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1829,7 +1853,7 @@
     <xdr:ext cx="3048000" cy="1819275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image112.jpg"/>
+        <xdr:cNvPr id="0" name="image26.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1885,7 +1909,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image16.jpg"/>
+        <xdr:cNvPr id="0" name="image113.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1913,7 +1937,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image34.jpg"/>
+        <xdr:cNvPr id="0" name="image60.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1941,7 +1965,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image103.jpg"/>
+        <xdr:cNvPr id="0" name="image47.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1969,7 +1993,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image49.jpg"/>
+        <xdr:cNvPr id="0" name="image11.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1997,7 +2021,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image18.jpg"/>
+        <xdr:cNvPr id="0" name="image8.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2025,7 +2049,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image40.jpg"/>
+        <xdr:cNvPr id="0" name="image29.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2053,7 +2077,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image22.jpg"/>
+        <xdr:cNvPr id="0" name="image23.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2081,7 +2105,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image113.jpg"/>
+        <xdr:cNvPr id="0" name="image36.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2109,7 +2133,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image19.jpg"/>
+        <xdr:cNvPr id="0" name="image45.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2137,7 +2161,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPr id="0" name="image62.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2165,7 +2189,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image118.jpg"/>
+        <xdr:cNvPr id="0" name="image28.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2193,7 +2217,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image20.jpg"/>
+        <xdr:cNvPr id="0" name="image34.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2221,7 +2245,7 @@
     <xdr:ext cx="2914650" cy="1819275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image108.jpg"/>
+        <xdr:cNvPr id="0" name="image76.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2246,10 +2270,10 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2914650" cy="1714500"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image106.jpg"/>
+    <xdr:ext cx="3048000" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image46.jpg" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2269,15 +2293,15 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3429000</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image8.jpg"/>
+        <xdr:cNvPr id="0" name="image18.jpg" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2305,7 +2329,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image42.jpg"/>
+        <xdr:cNvPr id="0" name="image30.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2333,7 +2357,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image35.jpg"/>
+        <xdr:cNvPr id="0" name="image40.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2361,7 +2385,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image114.jpg"/>
+        <xdr:cNvPr id="0" name="image35.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2389,7 +2413,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image27.jpg"/>
+        <xdr:cNvPr id="0" name="image37.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2417,7 +2441,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image109.jpg"/>
+        <xdr:cNvPr id="0" name="image118.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2445,7 +2469,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image11.jpg"/>
+        <xdr:cNvPr id="0" name="image56.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2473,7 +2497,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image28.jpg"/>
+        <xdr:cNvPr id="0" name="image43.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2501,7 +2525,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image15.jpg"/>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2529,7 +2553,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image31.jpg"/>
+        <xdr:cNvPr id="0" name="image16.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2557,7 +2581,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image43.jpg"/>
+        <xdr:cNvPr id="0" name="image15.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2585,7 +2609,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image17.jpg"/>
+        <xdr:cNvPr id="0" name="image119.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2613,7 +2637,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image29.jpg"/>
+        <xdr:cNvPr id="0" name="image24.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2641,7 +2665,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image65.jpg"/>
+        <xdr:cNvPr id="0" name="image94.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2669,7 +2693,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image36.jpg"/>
+        <xdr:cNvPr id="0" name="image31.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2697,7 +2721,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image10.jpg"/>
+        <xdr:cNvPr id="0" name="image65.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2725,7 +2749,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image25.jpg"/>
+        <xdr:cNvPr id="0" name="image19.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2753,7 +2777,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image14.jpg"/>
+        <xdr:cNvPr id="0" name="image41.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2781,7 +2805,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image24.jpg"/>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2809,7 +2833,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPr id="0" name="image25.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2837,7 +2861,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image39.jpg"/>
+        <xdr:cNvPr id="0" name="image20.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2865,7 +2889,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image7.jpg"/>
+        <xdr:cNvPr id="0" name="image82.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2893,7 +2917,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image115.jpg"/>
+        <xdr:cNvPr id="0" name="image101.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2921,7 +2945,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image21.jpg"/>
+        <xdr:cNvPr id="0" name="image12.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2949,7 +2973,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image52.jpg"/>
+        <xdr:cNvPr id="0" name="image22.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2977,7 +3001,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image26.jpg"/>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3005,7 +3029,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image111.jpg"/>
+        <xdr:cNvPr id="0" name="image17.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3033,7 +3057,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image23.jpg"/>
+        <xdr:cNvPr id="0" name="image13.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3061,7 +3085,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image37.jpg"/>
+        <xdr:cNvPr id="0" name="image10.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3089,7 +3113,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image47.jpg"/>
+        <xdr:cNvPr id="0" name="image38.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3117,7 +3141,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image44.jpg"/>
+        <xdr:cNvPr id="0" name="image93.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3145,7 +3169,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image71.jpg"/>
+        <xdr:cNvPr id="0" name="image42.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3173,7 +3197,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image50.jpg"/>
+        <xdr:cNvPr id="0" name="image48.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3201,7 +3225,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image41.jpg"/>
+        <xdr:cNvPr id="0" name="image99.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3229,7 +3253,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image48.jpg"/>
+        <xdr:cNvPr id="0" name="image59.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3257,7 +3281,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image75.jpg"/>
+        <xdr:cNvPr id="0" name="image63.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3285,7 +3309,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image58.jpg"/>
+        <xdr:cNvPr id="0" name="image70.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3313,7 +3337,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image46.jpg"/>
+        <xdr:cNvPr id="0" name="image72.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3341,7 +3365,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image80.jpg"/>
+        <xdr:cNvPr id="0" name="image49.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3369,7 +3393,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image121.jpg"/>
+        <xdr:cNvPr id="0" name="image52.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3397,7 +3421,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image56.jpg"/>
+        <xdr:cNvPr id="0" name="image83.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3425,7 +3449,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image51.jpg"/>
+        <xdr:cNvPr id="0" name="image61.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3453,7 +3477,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image59.jpg"/>
+        <xdr:cNvPr id="0" name="image54.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3481,7 +3505,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image60.jpg"/>
+        <xdr:cNvPr id="0" name="image50.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3509,7 +3533,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image55.jpg"/>
+        <xdr:cNvPr id="0" name="image127.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3537,7 +3561,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image53.jpg"/>
+        <xdr:cNvPr id="0" name="image89.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3565,7 +3589,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image57.jpg"/>
+        <xdr:cNvPr id="0" name="image79.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3593,7 +3617,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image125.jpg"/>
+        <xdr:cNvPr id="0" name="image85.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3621,7 +3645,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image119.jpg"/>
+        <xdr:cNvPr id="0" name="image55.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3649,7 +3673,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image130.jpg"/>
+        <xdr:cNvPr id="0" name="image115.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3677,7 +3701,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image84.jpg"/>
+        <xdr:cNvPr id="0" name="image57.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3705,7 +3729,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image69.jpg"/>
+        <xdr:cNvPr id="0" name="image78.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3733,7 +3757,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image54.jpg"/>
+        <xdr:cNvPr id="0" name="image53.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3761,7 +3785,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image88.jpg"/>
+        <xdr:cNvPr id="0" name="image64.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3789,7 +3813,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image68.jpg"/>
+        <xdr:cNvPr id="0" name="image126.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3817,7 +3841,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image116.jpg"/>
+        <xdr:cNvPr id="0" name="image67.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3845,7 +3869,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image67.jpg"/>
+        <xdr:cNvPr id="0" name="image91.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3873,7 +3897,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image64.jpg"/>
+        <xdr:cNvPr id="0" name="image58.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3901,7 +3925,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image63.jpg"/>
+        <xdr:cNvPr id="0" name="image68.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3929,7 +3953,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image83.jpg"/>
+        <xdr:cNvPr id="0" name="image71.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3957,7 +3981,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image61.jpg"/>
+        <xdr:cNvPr id="0" name="image73.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3985,7 +4009,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image70.jpg"/>
+        <xdr:cNvPr id="0" name="image66.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4013,7 +4037,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image66.jpg"/>
+        <xdr:cNvPr id="0" name="image122.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4041,7 +4065,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image120.jpg"/>
+        <xdr:cNvPr id="0" name="image107.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4069,7 +4093,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image76.jpg"/>
+        <xdr:cNvPr id="0" name="image120.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4097,7 +4121,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image93.jpg"/>
+        <xdr:cNvPr id="0" name="image75.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4125,7 +4149,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image62.jpg"/>
+        <xdr:cNvPr id="0" name="image81.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4153,7 +4177,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image91.jpg"/>
+        <xdr:cNvPr id="0" name="image74.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4181,7 +4205,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image74.jpg"/>
+        <xdr:cNvPr id="0" name="image110.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4209,7 +4233,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image123.jpg"/>
+        <xdr:cNvPr id="0" name="image97.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4237,7 +4261,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image81.jpg"/>
+        <xdr:cNvPr id="0" name="image80.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4265,7 +4289,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image78.jpg"/>
+        <xdr:cNvPr id="0" name="image87.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4293,7 +4317,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image122.jpg"/>
+        <xdr:cNvPr id="0" name="image77.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4321,7 +4345,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image73.jpg"/>
+        <xdr:cNvPr id="0" name="image105.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4349,7 +4373,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image126.jpg"/>
+        <xdr:cNvPr id="0" name="image90.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4377,7 +4401,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image72.jpg"/>
+        <xdr:cNvPr id="0" name="image134.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4405,7 +4429,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image82.jpg"/>
+        <xdr:cNvPr id="0" name="image86.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4433,7 +4457,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image79.jpg"/>
+        <xdr:cNvPr id="0" name="image92.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4461,7 +4485,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image124.jpg"/>
+        <xdr:cNvPr id="0" name="image117.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4489,7 +4513,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image100.jpg"/>
+        <xdr:cNvPr id="0" name="image103.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4517,7 +4541,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image94.jpg"/>
+        <xdr:cNvPr id="0" name="image106.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4545,7 +4569,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image129.jpg"/>
+        <xdr:cNvPr id="0" name="image128.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4573,7 +4597,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image127.jpg"/>
+        <xdr:cNvPr id="0" name="image100.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4601,7 +4625,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image77.jpg"/>
+        <xdr:cNvPr id="0" name="image116.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4629,7 +4653,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image85.jpg"/>
+        <xdr:cNvPr id="0" name="image129.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4657,7 +4681,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image92.jpg"/>
+        <xdr:cNvPr id="0" name="image95.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4685,7 +4709,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image95.jpg"/>
+        <xdr:cNvPr id="0" name="image88.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4713,7 +4737,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image90.jpg"/>
+        <xdr:cNvPr id="0" name="image123.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4741,7 +4765,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image87.jpg"/>
+        <xdr:cNvPr id="0" name="image98.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4769,7 +4793,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image96.jpg"/>
+        <xdr:cNvPr id="0" name="image125.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4797,7 +4821,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image128.jpg"/>
+        <xdr:cNvPr id="0" name="image102.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4825,7 +4849,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image86.jpg"/>
+        <xdr:cNvPr id="0" name="image124.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4853,7 +4877,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image104.jpg"/>
+        <xdr:cNvPr id="0" name="image96.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4881,7 +4905,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image89.jpg"/>
+        <xdr:cNvPr id="0" name="image114.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4909,7 +4933,7 @@
     <xdr:ext cx="2914650" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image98.jpg"/>
+        <xdr:cNvPr id="0" name="image104.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4937,7 +4961,7 @@
     <xdr:ext cx="3152775" cy="1600200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image107.png"/>
+        <xdr:cNvPr id="0" name="image112.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4965,7 +4989,7 @@
     <xdr:ext cx="2914650" cy="1257300"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image117.png"/>
+        <xdr:cNvPr id="0" name="image108.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4993,7 +5017,7 @@
     <xdr:ext cx="2000250" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image97.jpg"/>
+        <xdr:cNvPr id="0" name="image130.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5021,7 +5045,7 @@
     <xdr:ext cx="1285875" cy="1714500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image101.jpg"/>
+        <xdr:cNvPr id="0" name="image111.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -5049,11 +5073,123 @@
     <xdr:ext cx="3257550" cy="1600200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image99.jpg"/>
+        <xdr:cNvPr id="0" name="image133.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip cstate="print" r:embed="rId130"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2914650" cy="1714500"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image109.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId131"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2914650" cy="1714500"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image121.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId132"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3257550" cy="1819275"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image132.png" title="이미지"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId133"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3324225" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image131.png" title="이미지"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId134"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5285,251 +5421,251 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>9</v>
+      <c r="A1" s="19" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
-      <c r="A3" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="15"/>
+      <c r="A3" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="21"/>
+      <c r="G3" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="21"/>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="17">
+      <c r="A4" s="23">
         <f>COUNTA($C$17:$C$516)</f>
-        <v>82</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="17">
+        <v>84</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="23">
         <f>COUNTIF($G$17:$G$516,"본편 엔딩")+2*COUNTIF($G$17:$G$516,"본편 및 DLC 엔딩")</f>
-        <v>42</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="18">
+        <v>43</v>
+      </c>
+      <c r="D4" s="21"/>
+      <c r="E4" s="24">
         <f>COUNTIF($B$5:$B$8,"&gt;0")</f>
         <v>2</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="18">
+      <c r="F4" s="21"/>
+      <c r="G4" s="24">
         <f>COUNTIF($G$5:$G$13,"&gt;0")-1+IF(COUNTIFS($B$17:$B$516,"&gt;=TPS",$B$17:$B$516,"&lt;TPS~")&gt;0,1,0)+IF(COUNTIFS($B$17:$B$516,"&gt;=MOBA",$B$17:$B$516,"&lt;MOBA~")&gt;0,1,0)+IF(COUNTIFS($B$17:$B$516,"&gt;=FPS",$B$17:$B$516,"&lt;FPS~")&gt;0,1,0)+IF(COUNTIFS($B$17:$B$516,"&gt;=스포츠",$B$17:$B$516,"&lt;스포츠~")&gt;0,1,0)+IF(COUNTIFS($B$17:$B$516,"&gt;=소셜",$B$17:$B$516,"&lt;소셜~")&gt;0,1,0)+IF(COUNTIFS($B$17:$B$516,"&gt;=리듬",$B$17:$B$516,"&lt;리듬~")&gt;0,1,0)+IF(COUNTIFS($B$17:$B$516,"&gt;=샌드박스",$B$17:$B$516,"&lt;샌드박스~")&gt;0,1,0)+IF(COUNTIFS($B$17:$B$516,"&gt;=레이싱",$B$17:$B$516,"&lt;레이싱~")&gt;0,1,0)</f>
         <v>16</v>
       </c>
-      <c r="H4" s="15"/>
+      <c r="H4" s="21"/>
     </row>
     <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="19">
+      <c r="A5" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="25">
         <f>COUNTIF($A$17:$A$516,"PC")+COUNTIF($A$17:$A$516,"PC / Mobile")</f>
-        <v>73</v>
-      </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="19">
+        <v>74</v>
+      </c>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="25">
         <f>COUNTIFS($B$17:$B$516,"&gt;=시뮬레이션",$B$17:$B$516,"&lt;시뮬레이션~")</f>
         <v>3</v>
       </c>
-      <c r="H5" s="23"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="19">
+      <c r="A6" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="25">
         <f>COUNTIF($A$17:$A$516,"Mobile")+COUNTIF($A$17:$A$516,"PC / Mobile")</f>
-        <v>12</v>
-      </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="G6" s="19">
+        <v>13</v>
+      </c>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="G6" s="25">
         <f>COUNTIFS($B$17:$B$516,"&gt;=RPG",$B$17:$B$516,"&lt;RPG~")</f>
         <v>4</v>
       </c>
-      <c r="H6" s="23"/>
+      <c r="H6" s="26"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7" s="19">
+      <c r="A7" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="25">
         <f>COUNTIF($A$17:$A$516,"Console")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="G7" s="19">
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="G7" s="25">
         <f>COUNTIFS($B$17:$B$516,"&gt;=MMORPG",$B$17:$B$516,"&lt;MMORPG~")</f>
-        <v>5</v>
-      </c>
-      <c r="H7" s="23"/>
+        <v>6</v>
+      </c>
+      <c r="H7" s="26"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="19">
+      <c r="A8" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="25">
         <f>COUNTIF($A$17:$A$516,"기타")</f>
         <v>0</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="G8" s="19">
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" s="25">
         <f>COUNTIFS($B$17:$B$516,"&gt;=전략",$B$17:$B$516,"&lt;전략~")</f>
         <v>5</v>
       </c>
-      <c r="H8" s="23"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="G9" s="19">
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" s="25">
         <f>COUNTIFS($B$17:$B$516,"&gt;=퍼즐",$B$17:$B$516,"&lt;퍼즐~")</f>
         <v>6</v>
       </c>
-      <c r="H9" s="23"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G10" s="19">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="25">
         <f>COUNTIFS($B$17:$B$516,"&gt;=생존",$B$17:$B$516,"&lt;생존~")</f>
         <v>10</v>
       </c>
-      <c r="H10" s="23"/>
+      <c r="H10" s="26"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" s="19">
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="G11" s="25">
         <f>COUNTIFS($B$17:$B$516,"&gt;=TPS",$B$17:$B$516,"&lt;TPS~")+COUNTIFS($B$17:$B$516,"&gt;=MOBA",$B$17:$B$516,"&lt;MOBA~")+COUNTIFS($B$17:$B$516,"&gt;=FPS",$B$17:$B$516,"&lt;FPS~")+COUNTIFS($B$17:$B$516,"&gt;=스포츠",$B$17:$B$516,"&lt;스포츠~")+COUNTIFS($B$17:$B$516,"&gt;=소셜",$B$17:$B$516,"&lt;소셜~")+COUNTIFS($B$17:$B$516,"&gt;=리듬",$B$17:$B$516,"&lt;리듬~")+COUNTIFS($B$17:$B$516,"&gt;=샌드박스",$B$17:$B$516,"&lt;샌드박스~")+COUNTIFS($B$17:$B$516,"&gt;=레이싱",$B$17:$B$516,"&lt;레이싱~")</f>
         <v>15</v>
       </c>
-      <c r="H11" s="23"/>
+      <c r="H11" s="26"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="G12" s="19">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="G12" s="25">
         <f>COUNTIFS($B$17:$B$516,"&gt;=어드벤처",$B$17:$B$516,"&lt;어드벤처~")</f>
-        <v>13</v>
-      </c>
-      <c r="H12" s="23"/>
+        <v>14</v>
+      </c>
+      <c r="H12" s="26"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="G13" s="19">
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="G13" s="25">
         <f>COUNTIFS($B$17:$B$516,"&gt;=액션",$B$17:$B$516,"&lt;액션~")</f>
         <v>21</v>
       </c>
-      <c r="H13" s="23"/>
+      <c r="H13" s="26"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="23"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="26"/>
     </row>
     <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16" ht="27.0" customHeight="1">
       <c r="A16" s="27" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C16" s="27" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H16" s="27" t="s">
         <v>5</v>
@@ -5537,2021 +5673,2051 @@
     </row>
     <row r="17" ht="28.5" customHeight="1">
       <c r="A17" s="28" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D17" s="30">
         <v>153.04097222222222</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" ht="28.5" customHeight="1">
       <c r="A18" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>136</v>
+        <v>119</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>140</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D18" s="33">
         <v>46.62083333333333</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G18" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="H18" s="14"/>
+      <c r="G18" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="H18" s="12"/>
     </row>
     <row r="19" ht="28.5" customHeight="1">
       <c r="A19" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>139</v>
+        <v>121</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D19" s="33">
         <v>46.544444444444444</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>142</v>
+        <v>144</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="20" ht="28.5" customHeight="1">
       <c r="A20" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>143</v>
+        <v>119</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>147</v>
       </c>
       <c r="C20" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E20" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="G20" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="E20" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>146</v>
+      <c r="H20" s="12" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="21" ht="28.5" customHeight="1">
       <c r="A21" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>147</v>
+        <v>119</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D21" s="33">
-        <v>4.141666666666667</v>
+        <v>4.191666666666666</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H21" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H21" s="12"/>
     </row>
     <row r="22" ht="28.5" customHeight="1">
       <c r="A22" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>147</v>
+        <v>119</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D22" s="33">
         <v>2.275</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H22" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H22" s="12"/>
     </row>
     <row r="23" ht="28.5" customHeight="1">
       <c r="A23" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B23" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="33">
+        <v>1.8708333333333333</v>
+      </c>
+      <c r="E23" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="C23" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="33">
-        <v>1.7541666666666667</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F23" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="H23" s="14"/>
+      <c r="G23" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" s="12"/>
     </row>
     <row r="24" ht="28.5" customHeight="1">
       <c r="A24" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>151</v>
+        <v>119</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D24" s="33">
         <v>1.4541666666666666</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H24" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H24" s="12"/>
     </row>
     <row r="25" ht="28.5" customHeight="1">
       <c r="A25" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>152</v>
+        <v>119</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>156</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D25" s="33">
         <v>1.4041666666666666</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H25" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H25" s="12"/>
     </row>
     <row r="26" ht="28.5" customHeight="1">
       <c r="A26" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>153</v>
+        <v>119</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D26" s="34">
         <v>1.3333333333333333</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="H26" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="12"/>
     </row>
     <row r="27" ht="28.5" customHeight="1">
       <c r="A27" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>154</v>
+        <v>119</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>158</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D27" s="33">
         <v>1.325</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="H27" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="H27" s="12"/>
     </row>
     <row r="28" ht="28.5" customHeight="1">
       <c r="A28" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>156</v>
+        <v>119</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>160</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D28" s="33">
         <v>1.1958333333333333</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H28" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H28" s="12"/>
     </row>
     <row r="29" ht="28.5" customHeight="1">
       <c r="A29" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>157</v>
+        <v>119</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>161</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D29" s="33">
         <v>1.175</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H29" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H29" s="12"/>
     </row>
     <row r="30" ht="28.5" customHeight="1">
       <c r="A30" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>156</v>
+        <v>119</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>160</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D30" s="33">
         <v>0.9625</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H30" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H30" s="12"/>
     </row>
     <row r="31" ht="28.5" customHeight="1">
       <c r="A31" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>158</v>
+        <v>119</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>162</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D31" s="33">
         <v>0.95</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H31" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H31" s="12"/>
     </row>
     <row r="32" ht="28.5" customHeight="1">
       <c r="A32" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>147</v>
+        <v>119</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D32" s="33">
         <v>0.925</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H32" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H32" s="12"/>
     </row>
     <row r="33" ht="28.5" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>160</v>
+        <v>163</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>164</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D33" s="35">
         <v>0.8333333333333334</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>26</v>
+        <v>144</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="34" ht="28.5" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>162</v>
+        <v>119</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>166</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D34" s="33">
         <v>0.8166666666666667</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H34" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H34" s="12"/>
     </row>
     <row r="35" ht="28.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>163</v>
+        <v>119</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D35" s="33">
         <v>0.7958333333333333</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H35" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H35" s="12"/>
     </row>
     <row r="36" ht="28.5" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>164</v>
+        <v>119</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D36" s="33">
         <v>0.6875</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="H36" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="H36" s="12"/>
     </row>
     <row r="37" ht="28.5" customHeight="1">
       <c r="A37" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>166</v>
+        <v>119</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>170</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D37" s="33">
         <v>0.6833333333333333</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>167</v>
+        <v>138</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="38" ht="28.5" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>168</v>
+        <v>121</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>172</v>
       </c>
       <c r="C38" s="32" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D38" s="34">
         <v>0.625</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="H38" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H38" s="12"/>
     </row>
     <row r="39" ht="28.5" customHeight="1">
       <c r="A39" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>170</v>
+        <v>119</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D39" s="33">
         <v>0.6125</v>
       </c>
       <c r="E39" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G39" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="H39" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="H39" s="12"/>
     </row>
     <row r="40" ht="28.5" customHeight="1">
       <c r="A40" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>172</v>
+        <v>119</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D40" s="33">
         <v>0.5375</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G40" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H40" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H40" s="12"/>
     </row>
     <row r="41" ht="28.5" customHeight="1">
       <c r="A41" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>174</v>
+        <v>119</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>178</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D41" s="34">
         <v>0.5</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G41" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="H41" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="H41" s="12"/>
     </row>
     <row r="42" ht="28.5" customHeight="1">
       <c r="A42" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>176</v>
+        <v>119</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>180</v>
       </c>
       <c r="C42" s="32" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D42" s="33">
         <v>0.49583333333333335</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H42" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H42" s="12"/>
     </row>
     <row r="43" ht="28.5" customHeight="1">
       <c r="A43" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>166</v>
+        <v>119</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>170</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D43" s="33">
         <v>0.49583333333333335</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G43" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H43" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H43" s="12"/>
     </row>
     <row r="44" ht="28.5" customHeight="1">
       <c r="A44" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>170</v>
+        <v>119</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="C44" s="32" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D44" s="33">
         <v>0.475</v>
       </c>
       <c r="E44" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F44" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="H44" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="H44" s="12"/>
     </row>
     <row r="45" ht="28.5" customHeight="1">
       <c r="A45" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>178</v>
+        <v>119</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>182</v>
       </c>
       <c r="C45" s="32" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D45" s="33">
         <v>0.4666666666666667</v>
       </c>
       <c r="E45" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F45" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G45" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H45" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H45" s="12"/>
     </row>
     <row r="46" ht="28.5" customHeight="1">
       <c r="A46" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>178</v>
+        <v>119</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>182</v>
       </c>
       <c r="C46" s="32" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D46" s="33">
         <v>0.38333333333333336</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F46" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H46" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H46" s="12"/>
     </row>
     <row r="47" ht="28.5" customHeight="1">
       <c r="A47" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>179</v>
+        <v>119</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>183</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D47" s="33">
         <v>0.37083333333333335</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F47" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G47" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H47" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H47" s="12"/>
     </row>
     <row r="48" ht="28.5" customHeight="1">
       <c r="A48" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>158</v>
+        <v>119</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>162</v>
       </c>
       <c r="C48" s="32" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D48" s="33">
         <v>0.36666666666666664</v>
       </c>
       <c r="E48" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F48" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H48" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H48" s="12"/>
     </row>
     <row r="49" ht="28.5" customHeight="1">
       <c r="A49" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>154</v>
+        <v>119</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>158</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D49" s="33">
         <v>0.3625</v>
       </c>
       <c r="E49" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F49" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G49" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="H49" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="H49" s="12"/>
     </row>
     <row r="50" ht="28.5" customHeight="1">
       <c r="A50" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>180</v>
+        <v>119</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="C50" s="32" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D50" s="33">
         <v>0.3625</v>
       </c>
       <c r="E50" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F50" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G50" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H50" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H50" s="12"/>
     </row>
     <row r="51" ht="28.5" customHeight="1">
       <c r="A51" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>181</v>
+        <v>119</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="C51" s="32" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D51" s="33">
         <v>0.3458333333333333</v>
       </c>
       <c r="E51" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F51" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G51" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H51" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H51" s="12"/>
     </row>
     <row r="52" ht="28.5" customHeight="1">
       <c r="A52" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C52" s="32" t="s">
         <v>105</v>
-      </c>
-      <c r="B52" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C52" s="32" t="s">
-        <v>113</v>
       </c>
       <c r="D52" s="34">
         <v>0.3333333333333333</v>
       </c>
       <c r="E52" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F52" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G52" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H52" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H52" s="12"/>
     </row>
     <row r="53" ht="28.5" customHeight="1">
       <c r="A53" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>154</v>
+        <v>119</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="C53" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="D53" s="33">
-        <v>0.32916666666666666</v>
+        <v>109</v>
+      </c>
+      <c r="D53" s="34">
+        <v>0.3333333333333333</v>
       </c>
       <c r="E53" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F53" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G53" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H53" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H53" s="12"/>
     </row>
     <row r="54" ht="28.5" customHeight="1">
       <c r="A54" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B54" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="12" t="s">
         <v>158</v>
       </c>
       <c r="C54" s="32" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="D54" s="33">
-        <v>0.32083333333333336</v>
+        <v>0.32916666666666666</v>
       </c>
       <c r="E54" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G54" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H54" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H54" s="12"/>
     </row>
     <row r="55" ht="28.5" customHeight="1">
       <c r="A55" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55" s="14" t="s">
-        <v>178</v>
+        <v>119</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>162</v>
       </c>
       <c r="C55" s="32" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="D55" s="33">
-        <v>0.3</v>
+        <v>0.32083333333333336</v>
       </c>
       <c r="E55" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F55" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G55" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H55" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H55" s="12"/>
     </row>
     <row r="56" ht="28.5" customHeight="1">
       <c r="A56" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>183</v>
+        <v>119</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>182</v>
       </c>
       <c r="C56" s="32" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D56" s="33">
         <v>0.3</v>
       </c>
       <c r="E56" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F56" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G56" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H56" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H56" s="12"/>
     </row>
     <row r="57" ht="28.5" customHeight="1">
       <c r="A57" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>184</v>
+        <v>119</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D57" s="33">
-        <v>0.2625</v>
+        <v>0.3</v>
       </c>
       <c r="E57" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F57" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G57" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H57" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H57" s="12"/>
     </row>
     <row r="58" ht="28.5" customHeight="1">
       <c r="A58" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="C58" s="32" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="D58" s="33">
-        <v>0.2590277777777778</v>
+        <v>0.2625</v>
       </c>
       <c r="E58" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F58" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G58" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="H58" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G58" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H58" s="12"/>
     </row>
     <row r="59" ht="28.5" customHeight="1">
       <c r="A59" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>186</v>
+        <v>121</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C59" s="32" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D59" s="33">
-        <v>0.2</v>
+        <v>0.2590277777777778</v>
       </c>
       <c r="E59" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F59" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G59" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="H59" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="G59" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="H59" s="12"/>
     </row>
     <row r="60" ht="28.5" customHeight="1">
       <c r="A60" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>180</v>
+        <v>119</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="C60" s="32" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="D60" s="33">
         <v>0.2</v>
       </c>
       <c r="E60" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F60" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G60" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H60" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G60" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="H60" s="12"/>
     </row>
     <row r="61" ht="28.5" customHeight="1">
       <c r="A61" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>186</v>
+        <v>119</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D61" s="33">
-        <v>0.17916666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="E61" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F61" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G61" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H61" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H61" s="12"/>
     </row>
     <row r="62" ht="28.5" customHeight="1">
       <c r="A62" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B62" s="14" t="s">
-        <v>187</v>
+        <v>119</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="C62" s="32" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D62" s="33">
         <v>0.17916666666666667</v>
       </c>
       <c r="E62" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G62" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H62" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H62" s="12"/>
     </row>
     <row r="63" ht="28.5" customHeight="1">
       <c r="A63" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>188</v>
+        <v>119</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="C63" s="32" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D63" s="33">
-        <v>0.175</v>
+        <v>0.17916666666666667</v>
       </c>
       <c r="E63" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F63" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G63" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H63" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H63" s="12"/>
     </row>
     <row r="64" ht="28.5" customHeight="1">
       <c r="A64" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>189</v>
+        <v>119</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>193</v>
       </c>
       <c r="C64" s="32" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="D64" s="33">
         <v>0.175</v>
       </c>
       <c r="E64" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F64" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G64" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="H64" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G64" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H64" s="12"/>
     </row>
     <row r="65" ht="28.5" customHeight="1">
       <c r="A65" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B65" s="14" t="s">
-        <v>191</v>
+        <v>119</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>194</v>
       </c>
       <c r="C65" s="32" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D65" s="33">
-        <v>0.17083333333333334</v>
+        <v>0.175</v>
       </c>
       <c r="E65" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F65" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G65" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="H65" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="H65" s="12"/>
     </row>
     <row r="66" ht="28.5" customHeight="1">
       <c r="A66" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B66" s="14" t="s">
-        <v>192</v>
+        <v>119</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>196</v>
       </c>
       <c r="C66" s="32" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="D66" s="33">
-        <v>0.1625</v>
+        <v>0.17083333333333334</v>
       </c>
       <c r="E66" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F66" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G66" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="H66" s="14" t="s">
-        <v>194</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="G66" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="H66" s="12"/>
     </row>
     <row r="67" ht="28.5" customHeight="1">
       <c r="A67" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B67" s="14" t="s">
-        <v>192</v>
+        <v>119</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>197</v>
       </c>
       <c r="C67" s="32" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="D67" s="33">
         <v>0.1625</v>
       </c>
       <c r="E67" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F67" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G67" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="H67" s="14" t="s">
-        <v>195</v>
+        <v>138</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="H67" s="12" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="68" ht="28.5" customHeight="1">
       <c r="A68" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>187</v>
+        <v>119</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>197</v>
       </c>
       <c r="C68" s="32" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D68" s="33">
-        <v>0.15</v>
+        <v>0.1625</v>
       </c>
       <c r="E68" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F68" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G68" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H68" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="H68" s="12" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="69" ht="28.5" customHeight="1">
       <c r="A69" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B69" s="14" t="s">
-        <v>196</v>
+        <v>119</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="C69" s="32" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D69" s="33">
         <v>0.15</v>
       </c>
       <c r="E69" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F69" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G69" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="H69" s="14" t="s">
-        <v>197</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H69" s="12"/>
     </row>
     <row r="70" ht="28.5" customHeight="1">
       <c r="A70" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B70" s="14" t="s">
-        <v>187</v>
+        <v>119</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="C70" s="32" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="D70" s="33">
-        <v>0.14583333333333334</v>
+        <v>0.15</v>
       </c>
       <c r="E70" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F70" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G70" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="H70" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G70" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="H70" s="12" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="71" ht="28.5" customHeight="1">
       <c r="A71" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B71" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C71" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" s="33">
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="E71" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="F71" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G71" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="C71" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D71" s="33">
-        <v>0.14166666666666666</v>
-      </c>
-      <c r="E71" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F71" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G71" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H71" s="14"/>
+      <c r="H71" s="12"/>
     </row>
     <row r="72" ht="28.5" customHeight="1">
       <c r="A72" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>183</v>
+        <v>119</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>203</v>
       </c>
       <c r="C72" s="32" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="D72" s="33">
         <v>0.14166666666666666</v>
       </c>
       <c r="E72" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F72" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G72" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H72" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G72" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H72" s="12"/>
     </row>
     <row r="73" ht="28.5" customHeight="1">
       <c r="A73" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>199</v>
+        <v>119</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>188</v>
       </c>
       <c r="C73" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="D73" s="34">
-        <v>0.125</v>
+        <v>86</v>
+      </c>
+      <c r="D73" s="33">
+        <v>0.14166666666666666</v>
       </c>
       <c r="E73" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F73" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G73" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="H73" s="14" t="s">
-        <v>26</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H73" s="12"/>
     </row>
     <row r="74" ht="28.5" customHeight="1">
       <c r="A74" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B74" s="14" t="s">
-        <v>201</v>
+        <v>119</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="C74" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="D74" s="33">
-        <v>0.11666666666666667</v>
+        <v>46</v>
+      </c>
+      <c r="D74" s="34">
+        <v>0.125</v>
       </c>
       <c r="E74" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F74" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G74" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="H74" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="75" ht="28.5" customHeight="1">
       <c r="A75" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B75" s="14" t="s">
-        <v>202</v>
+        <v>119</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="C75" s="32" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D75" s="33">
-        <v>0.1125</v>
+        <v>0.11666666666666667</v>
       </c>
       <c r="E75" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F75" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G75" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="H75" s="14" t="s">
-        <v>195</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="H75" s="12"/>
     </row>
     <row r="76" ht="28.5" customHeight="1">
       <c r="A76" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>203</v>
+        <v>119</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>207</v>
       </c>
       <c r="C76" s="32" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="D76" s="33">
         <v>0.1125</v>
       </c>
       <c r="E76" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F76" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G76" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H76" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="G76" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="H76" s="12" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="77" ht="28.5" customHeight="1">
       <c r="A77" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B77" s="14" t="s">
-        <v>178</v>
+        <v>119</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="C77" s="32" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D77" s="33">
         <v>0.1125</v>
       </c>
       <c r="E77" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F77" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G77" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H77" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H77" s="12"/>
     </row>
     <row r="78" ht="28.5" customHeight="1">
       <c r="A78" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>204</v>
+        <v>119</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>182</v>
       </c>
       <c r="C78" s="32" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="D78" s="33">
-        <v>0.10694444444444444</v>
+        <v>0.1125</v>
       </c>
       <c r="E78" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F78" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G78" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="H78" s="14" t="s">
-        <v>26</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="G78" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H78" s="12"/>
     </row>
     <row r="79" ht="28.5" customHeight="1">
       <c r="A79" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>206</v>
+        <v>119</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>209</v>
       </c>
       <c r="C79" s="32" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D79" s="33">
-        <v>0.10416666666666667</v>
+        <v>0.10694444444444444</v>
       </c>
       <c r="E79" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F79" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G79" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H79" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="80" ht="28.5" customHeight="1">
       <c r="A80" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B80" s="14" t="s">
-        <v>154</v>
+        <v>119</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="C80" s="32" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="D80" s="33">
-        <v>0.1</v>
+        <v>0.10416666666666667</v>
       </c>
       <c r="E80" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F80" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G80" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="H80" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G80" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H80" s="12"/>
     </row>
     <row r="81" ht="28.5" customHeight="1">
       <c r="A81" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>207</v>
+        <v>119</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>158</v>
       </c>
       <c r="C81" s="32" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="D81" s="33">
-        <v>0.09166666666666666</v>
+        <v>0.1</v>
       </c>
       <c r="E81" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F81" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G81" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H81" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="G81" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="H81" s="12"/>
     </row>
     <row r="82" ht="28.5" customHeight="1">
       <c r="A82" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B82" s="14" t="s">
-        <v>208</v>
+        <v>119</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="C82" s="32" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="D82" s="33">
-        <v>0.06736111111111111</v>
+        <v>0.09166666666666666</v>
       </c>
       <c r="E82" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F82" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G82" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H82" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="G82" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H82" s="12"/>
     </row>
     <row r="83" ht="28.5" customHeight="1">
       <c r="A83" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B83" s="14" t="s">
-        <v>209</v>
+        <v>119</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="C83" s="32" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D83" s="33">
-        <v>0.06388888888888888</v>
+        <v>0.06736111111111111</v>
       </c>
       <c r="E83" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F83" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G83" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="H83" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G83" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H83" s="12"/>
     </row>
     <row r="84" ht="28.5" customHeight="1">
       <c r="A84" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B84" s="14" t="s">
-        <v>210</v>
+        <v>119</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>214</v>
       </c>
       <c r="C84" s="32" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="D84" s="33">
-        <v>0.05138888888888889</v>
+        <v>0.06388888888888888</v>
       </c>
       <c r="E84" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F84" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G84" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H84" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G84" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="H84" s="12"/>
     </row>
     <row r="85" ht="28.5" customHeight="1">
       <c r="A85" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B85" s="14" t="s">
-        <v>211</v>
+        <v>119</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="C85" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="D85" s="36">
-        <v>0.04097222222222222</v>
+        <v>6</v>
+      </c>
+      <c r="D85" s="33">
+        <v>0.05138888888888889</v>
       </c>
       <c r="E85" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F85" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G85" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="H85" s="14" t="s">
-        <v>195</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="G85" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H85" s="12"/>
     </row>
     <row r="86" ht="28.5" customHeight="1">
       <c r="A86" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B86" s="14" t="s">
-        <v>212</v>
+        <v>119</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>216</v>
       </c>
       <c r="C86" s="32" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="D86" s="36">
-        <v>0.035416666666666666</v>
+        <v>0.04097222222222222</v>
       </c>
       <c r="E86" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F86" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G86" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="H86" s="14" t="s">
-        <v>26</v>
+        <v>138</v>
+      </c>
+      <c r="G86" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="H86" s="12" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="87" ht="28.5" customHeight="1">
       <c r="A87" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B87" s="14" t="s">
-        <v>181</v>
+        <v>121</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="C87" s="32" t="s">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="D87" s="36">
-        <v>0.02638888888888889</v>
+        <v>0.035416666666666666</v>
       </c>
       <c r="E87" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F87" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G87" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="H87" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="G87" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="H87" s="12" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="88" ht="28.5" customHeight="1">
       <c r="A88" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B88" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="C88" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="D88" s="31" t="s">
-        <v>144</v>
+        <v>65</v>
+      </c>
+      <c r="D88" s="36">
+        <v>0.02638888888888889</v>
       </c>
       <c r="E88" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F88" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G88" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="H88" s="14" t="s">
-        <v>26</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="G88" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="H88" s="12"/>
     </row>
     <row r="89" ht="28.5" customHeight="1">
       <c r="A89" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="B89" s="14" t="s">
-        <v>174</v>
+        <v>121</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C89" s="32" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="D89" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E89" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="F89" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="E89" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F89" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G89" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="H89" s="14"/>
+      <c r="G89" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="H89" s="12" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="90" ht="28.5" customHeight="1">
       <c r="A90" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B90" s="14" t="s">
-        <v>215</v>
+        <v>163</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>178</v>
       </c>
       <c r="C90" s="32" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D90" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E90" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="F90" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="E90" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F90" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G90" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H90" s="14"/>
+      <c r="G90" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" s="12"/>
     </row>
     <row r="91" ht="28.5" customHeight="1">
       <c r="A91" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="B91" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>220</v>
       </c>
       <c r="C91" s="32" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D91" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E91" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="F91" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="E91" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F91" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G91" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="H91" s="14"/>
+      <c r="G91" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H91" s="12"/>
     </row>
     <row r="92" ht="28.5" customHeight="1">
       <c r="A92" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>217</v>
+        <v>163</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C92" s="32" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D92" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E92" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="F92" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="E92" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F92" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G92" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H92" s="14"/>
+      <c r="G92" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="H92" s="12"/>
     </row>
     <row r="93" ht="28.5" customHeight="1">
       <c r="A93" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B93" s="14" t="s">
-        <v>218</v>
+        <v>121</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="C93" s="32" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D93" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E93" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F93" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G93" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="H93" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G93" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H93" s="12"/>
     </row>
     <row r="94" ht="28.5" customHeight="1">
       <c r="A94" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B94" s="14" t="s">
-        <v>219</v>
+        <v>119</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="C94" s="32" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D94" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E94" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="F94" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="E94" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F94" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G94" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="H94" s="14"/>
+      <c r="G94" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H94" s="12"/>
     </row>
     <row r="95" ht="28.5" customHeight="1">
       <c r="A95" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>221</v>
+        <v>121</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="C95" s="32" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="D95" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E95" s="31" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F95" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G95" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="H95" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G95" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="H95" s="12"/>
     </row>
     <row r="96" ht="28.5" customHeight="1">
       <c r="A96" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>222</v>
+        <v>121</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>226</v>
       </c>
       <c r="C96" s="32" t="s">
-        <v>223</v>
+        <v>61</v>
       </c>
       <c r="D96" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E96" s="31" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F96" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G96" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="H96" s="14" t="s">
-        <v>225</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="G96" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H96" s="12"/>
     </row>
     <row r="97" ht="28.5" customHeight="1">
       <c r="A97" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B97" s="14" t="s">
-        <v>226</v>
+        <v>119</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>227</v>
       </c>
       <c r="C97" s="32" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D97" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E97" s="31" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F97" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G97" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="H97" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="G97" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="H97" s="12" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="98" ht="28.5" customHeight="1">
       <c r="A98" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>229</v>
+        <v>119</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="C98" s="32" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D98" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E98" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="F98" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G98" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="H98" s="12"/>
+    </row>
+    <row r="99" ht="28.5" customHeight="1">
+      <c r="A99" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C99" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="D99" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E99" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="F99" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G99" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="H99" s="12"/>
+    </row>
+    <row r="100" ht="28.5" customHeight="1">
+      <c r="A100" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="C100" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="D100" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E100" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="F100" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="E98" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="F98" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G98" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="H98" s="14"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="37"/>
-      <c r="B99" s="38"/>
-      <c r="C99" s="38"/>
-      <c r="D99" s="37"/>
-      <c r="E99" s="37"/>
-      <c r="F99" s="37"/>
-      <c r="G99" s="38"/>
-      <c r="H99" s="38"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="37"/>
-      <c r="B100" s="38"/>
-      <c r="C100" s="38"/>
-      <c r="D100" s="37"/>
-      <c r="E100" s="37"/>
-      <c r="F100" s="37"/>
-      <c r="G100" s="38"/>
-      <c r="H100" s="38"/>
+      <c r="G100" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="H100" s="12" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="37"/>
@@ -9485,43 +9651,43 @@
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="39"/>
-      <c r="B294" s="23"/>
-      <c r="C294" s="23"/>
-      <c r="D294" s="23"/>
+      <c r="B294" s="26"/>
+      <c r="C294" s="26"/>
+      <c r="D294" s="26"/>
       <c r="E294" s="39"/>
       <c r="F294" s="39"/>
-      <c r="G294" s="23"/>
-      <c r="H294" s="23"/>
+      <c r="G294" s="26"/>
+      <c r="H294" s="26"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="39"/>
-      <c r="B295" s="23"/>
-      <c r="C295" s="23"/>
-      <c r="D295" s="23"/>
+      <c r="B295" s="26"/>
+      <c r="C295" s="26"/>
+      <c r="D295" s="26"/>
       <c r="E295" s="39"/>
       <c r="F295" s="39"/>
-      <c r="G295" s="23"/>
-      <c r="H295" s="23"/>
+      <c r="G295" s="26"/>
+      <c r="H295" s="26"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="39"/>
-      <c r="B296" s="23"/>
-      <c r="C296" s="23"/>
-      <c r="D296" s="23"/>
+      <c r="B296" s="26"/>
+      <c r="C296" s="26"/>
+      <c r="D296" s="26"/>
       <c r="E296" s="39"/>
       <c r="F296" s="39"/>
-      <c r="G296" s="23"/>
-      <c r="H296" s="23"/>
+      <c r="G296" s="26"/>
+      <c r="H296" s="26"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="39"/>
-      <c r="B297" s="23"/>
-      <c r="C297" s="23"/>
-      <c r="D297" s="23"/>
+      <c r="B297" s="26"/>
+      <c r="C297" s="26"/>
+      <c r="D297" s="26"/>
       <c r="E297" s="39"/>
       <c r="F297" s="39"/>
-      <c r="G297" s="23"/>
-      <c r="H297" s="23"/>
+      <c r="G297" s="26"/>
+      <c r="H297" s="26"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="40"/>
@@ -9529,14 +9695,14 @@
       <c r="F298" s="40"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="41"/>
-      <c r="E299" s="41"/>
-      <c r="F299" s="41"/>
+      <c r="A299" s="40"/>
+      <c r="E299" s="40"/>
+      <c r="F299" s="40"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="41"/>
-      <c r="E300" s="41"/>
-      <c r="F300" s="41"/>
+      <c r="A300" s="40"/>
+      <c r="E300" s="40"/>
+      <c r="F300" s="40"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="41"/>
@@ -11186,778 +11352,796 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="148.5" customHeight="1">
+      <c r="A6" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" ht="148.5" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="14" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" ht="148.5" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
-      <c r="D7" s="10" t="s">
-        <v>17</v>
+      <c r="D7" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="148.5" customHeight="1">
-      <c r="A8" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="14" t="s">
-        <v>19</v>
+      <c r="A8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="12" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" ht="148.5" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="10" t="s">
-        <v>22</v>
+      <c r="D9" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="148.5" customHeight="1">
-      <c r="A10" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="14" t="s">
-        <v>24</v>
+      <c r="A10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="148.5" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
-      <c r="D11" s="10" t="s">
-        <v>26</v>
+      <c r="D11" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="148.5" customHeight="1">
-      <c r="A12" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="14" t="s">
-        <v>29</v>
+      <c r="A12" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" ht="148.5" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="10" t="s">
-        <v>31</v>
+      <c r="D13" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="148.5" customHeight="1">
-      <c r="A14" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="14" t="s">
-        <v>33</v>
+      <c r="A14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" ht="148.5" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="10" t="s">
-        <v>35</v>
+      <c r="D15" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="148.5" customHeight="1">
-      <c r="A16" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="14" t="s">
-        <v>37</v>
+      <c r="A16" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="17" ht="148.5" customHeight="1">
       <c r="A17" s="7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="10" t="s">
-        <v>26</v>
+      <c r="D17" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="18" ht="148.5" customHeight="1">
-      <c r="A18" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="14" t="s">
+      <c r="A18" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" ht="148.5" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" ht="148.5" customHeight="1">
-      <c r="A20" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="14" t="s">
+      <c r="A20" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" ht="148.5" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" ht="148.5" customHeight="1">
-      <c r="A22" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="14" t="s">
+      <c r="A22" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="23" ht="148.5" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" ht="148.5" customHeight="1">
-      <c r="A24" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="14" t="s">
-        <v>46</v>
+      <c r="A24" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="12" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="25" ht="148.5" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="10" t="s">
-        <v>48</v>
+      <c r="D25" s="9" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="26" ht="148.5" customHeight="1">
-      <c r="A26" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="14" t="s">
+      <c r="A26" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" ht="148.5" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="28" ht="148.5" customHeight="1">
-      <c r="A28" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="14" t="s">
+      <c r="A28" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="29" ht="148.5" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="10" t="s">
-        <v>53</v>
+      <c r="D29" s="9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30" ht="148.5" customHeight="1">
-      <c r="A30" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="14" t="s">
+      <c r="A30" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" ht="148.5" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" ht="148.5" customHeight="1">
-      <c r="A32" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="14" t="s">
+      <c r="A32" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" ht="148.5" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="10" t="s">
-        <v>58</v>
+      <c r="D33" s="9" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="34" ht="148.5" customHeight="1">
-      <c r="A34" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="14" t="s">
+      <c r="A34" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="35" ht="148.5" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="10" t="s">
-        <v>61</v>
+      <c r="D35" s="9" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="36" ht="148.5" customHeight="1">
-      <c r="A36" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="14" t="s">
+      <c r="A36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="37" ht="148.5" customHeight="1">
       <c r="A37" s="7" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="38" ht="148.5" customHeight="1">
-      <c r="A38" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="14" t="s">
+      <c r="A38" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="39" ht="148.5" customHeight="1">
       <c r="A39" s="7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="40" ht="148.5" customHeight="1">
-      <c r="A40" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="14" t="s">
+      <c r="A40" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="41" ht="148.5" customHeight="1">
       <c r="A41" s="7" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
-      <c r="D41" s="10" t="s">
-        <v>68</v>
+      <c r="D41" s="9" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="42" ht="148.5" customHeight="1">
-      <c r="A42" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="14" t="s">
+      <c r="A42" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="43" ht="148.5" customHeight="1">
       <c r="A43" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="44" ht="148.5" customHeight="1">
-      <c r="A44" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="14" t="s">
+      <c r="A44" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="45" ht="148.5" customHeight="1">
       <c r="A45" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="46" ht="148.5" customHeight="1">
-      <c r="A46" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="14" t="s">
+      <c r="A46" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="47" ht="148.5" customHeight="1">
       <c r="A47" s="7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="48" ht="148.5" customHeight="1">
-      <c r="A48" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="14" t="s">
+      <c r="A48" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="49" ht="148.5" customHeight="1">
       <c r="A49" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="50" ht="148.5" customHeight="1">
-      <c r="A50" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="14" t="s">
+      <c r="A50" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="51" ht="148.5" customHeight="1">
       <c r="A51" s="7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="52" ht="148.5" customHeight="1">
-      <c r="A52" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="14" t="s">
+      <c r="A52" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="53" ht="148.5" customHeight="1">
       <c r="A53" s="7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="54" ht="148.5" customHeight="1">
-      <c r="A54" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="14" t="s">
+      <c r="A54" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="55" ht="148.5" customHeight="1">
       <c r="A55" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
-      <c r="D55" s="10" t="s">
-        <v>83</v>
+      <c r="D55" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="56" ht="148.5" customHeight="1">
-      <c r="A56" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="14" t="s">
+      <c r="A56" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="57" ht="148.5" customHeight="1">
       <c r="A57" s="7" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
-      <c r="D57" s="10" t="s">
+      <c r="D57" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="58" ht="148.5" customHeight="1">
-      <c r="A58" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="14" t="s">
+      <c r="A58" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="59" ht="148.5" customHeight="1">
       <c r="A59" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
-      <c r="D59" s="10" t="s">
+      <c r="D59" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="60" ht="148.5" customHeight="1">
-      <c r="A60" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="14" t="s">
+      <c r="A60" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="61" ht="148.5" customHeight="1">
       <c r="A61" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
-      <c r="D61" s="10" t="s">
+      <c r="D61" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="62" ht="148.5" customHeight="1">
-      <c r="A62" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="14" t="s">
+      <c r="A62" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="63" ht="148.5" customHeight="1">
       <c r="A63" s="7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
-      <c r="D63" s="10" t="s">
+      <c r="D63" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="64" ht="148.5" customHeight="1">
-      <c r="A64" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="14" t="s">
+      <c r="A64" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="65" ht="148.5" customHeight="1">
       <c r="A65" s="7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
-      <c r="D65" s="10" t="s">
+      <c r="D65" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="66" ht="148.5" customHeight="1">
-      <c r="A66" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="14" t="s">
+      <c r="A66" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="67" ht="148.5" customHeight="1">
       <c r="A67" s="7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
-      <c r="D67" s="10" t="s">
-        <v>96</v>
+      <c r="D67" s="9" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="68" ht="148.5" customHeight="1">
-      <c r="A68" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="14" t="s">
+      <c r="A68" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="69" ht="148.5" customHeight="1">
       <c r="A69" s="7" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
-      <c r="D69" s="10" t="s">
+      <c r="D69" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="70" ht="148.5" customHeight="1">
-      <c r="A70" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="14" t="s">
+      <c r="A70" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="71" ht="148.5" customHeight="1">
       <c r="A71" s="7" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
-      <c r="D71" s="10" t="s">
+      <c r="D71" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="72" ht="148.5" customHeight="1">
-      <c r="A72" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="14" t="s">
+      <c r="A72" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="73" ht="148.5" customHeight="1">
       <c r="A73" s="7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
-      <c r="D73" s="10" t="s">
+      <c r="D73" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="74" ht="148.5" customHeight="1">
-      <c r="A74" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="14" t="s">
+      <c r="A74" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="75" ht="148.5" customHeight="1">
       <c r="A75" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
-      <c r="D75" s="10" t="s">
+      <c r="D75" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="76" ht="148.5" customHeight="1">
-      <c r="A76" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="14" t="s">
+      <c r="A76" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="77" ht="148.5" customHeight="1">
       <c r="A77" s="7" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
-      <c r="D77" s="10" t="s">
+      <c r="D77" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="78" ht="148.5" customHeight="1">
-      <c r="A78" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B78" s="12"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="14" t="s">
-        <v>109</v>
+      <c r="A78" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="79" ht="148.5" customHeight="1">
       <c r="A79" s="7" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
-      <c r="D79" s="10" t="s">
+      <c r="D79" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="80" ht="148.5" customHeight="1">
-      <c r="A80" s="20" t="s">
+      <c r="A80" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B80" s="14"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" ht="148.5" customHeight="1">
+      <c r="A81" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D81" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="82" ht="148.5" customHeight="1">
+      <c r="A82" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="83" ht="148.5" customHeight="1">
+      <c r="A83" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D83" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+    </row>
+    <row r="84" ht="148.5" customHeight="1">
+      <c r="A84" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B80" s="21"/>
-      <c r="C80" s="21"/>
-      <c r="D80" s="22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" ht="148.5" customHeight="1">
-      <c r="A81" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D81" s="25" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="82" ht="148.5" customHeight="1">
-      <c r="A82" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D82" s="26" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
+      <c r="D84" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+    </row>
     <row r="85" ht="15.75" customHeight="1"/>
     <row r="86" ht="15.75" customHeight="1"/>
     <row r="87" ht="15.75" customHeight="1"/>
